--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 09/top view/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 09/top view/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.61999</v>
+        <v>16.65967</v>
       </c>
       <c r="D2" t="n">
-        <v>16.65983</v>
+        <v>15.84105</v>
       </c>
       <c r="E2" t="n">
-        <v>16.77236</v>
+        <v>16.1045</v>
       </c>
       <c r="F2" t="n">
-        <v>41.99739</v>
+        <v>41.91697</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04903</v>
+        <v>0.0498</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78457</v>
+        <v>1.78387</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.81962</v>
+        <v>16.4164</v>
       </c>
       <c r="D3" t="n">
-        <v>16.3568</v>
+        <v>16.26708</v>
       </c>
       <c r="E3" t="n">
-        <v>16.29776</v>
+        <v>16.3338</v>
       </c>
       <c r="F3" t="n">
-        <v>40.91667</v>
+        <v>42.62477</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04943</v>
+        <v>0.05089</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81785</v>
+        <v>1.79974</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.71771</v>
+        <v>16.57926</v>
       </c>
       <c r="D4" t="n">
-        <v>16.51068</v>
+        <v>16.38348</v>
       </c>
       <c r="E4" t="n">
-        <v>16.51792</v>
+        <v>16.42899</v>
       </c>
       <c r="F4" t="n">
-        <v>41.62653</v>
+        <v>42.7669</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05069</v>
+        <v>0.05084</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78222</v>
+        <v>1.79747</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.77909</v>
+        <v>16.49205</v>
       </c>
       <c r="D5" t="n">
-        <v>16.69533</v>
+        <v>16.077</v>
       </c>
       <c r="E5" t="n">
-        <v>16.37714</v>
+        <v>16.1229</v>
       </c>
       <c r="F5" t="n">
-        <v>42.9777</v>
+        <v>42.25728</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05016</v>
+        <v>0.05061</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82494</v>
+        <v>1.8133</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.38015</v>
+        <v>16.67574</v>
       </c>
       <c r="D6" t="n">
-        <v>16.42508</v>
+        <v>16.47215</v>
       </c>
       <c r="E6" t="n">
-        <v>17.06515</v>
+        <v>16.49037</v>
       </c>
       <c r="F6" t="n">
-        <v>41.82981</v>
+        <v>42.48186</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05061</v>
+        <v>0.05077</v>
       </c>
       <c r="H6" t="n">
-        <v>1.80511</v>
+        <v>1.7812</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.93523</v>
+        <v>16.64409</v>
       </c>
       <c r="D7" t="n">
-        <v>16.32128</v>
+        <v>16.20334</v>
       </c>
       <c r="E7" t="n">
-        <v>15.8706</v>
+        <v>16.60717</v>
       </c>
       <c r="F7" t="n">
-        <v>41.601</v>
+        <v>42.43376</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0488</v>
+        <v>0.05026</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83029</v>
+        <v>1.79935</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.7261</v>
+        <v>16.64584</v>
       </c>
       <c r="D8" t="n">
-        <v>16.29927</v>
+        <v>16.33017</v>
       </c>
       <c r="E8" t="n">
-        <v>16.48982</v>
+        <v>16.60893</v>
       </c>
       <c r="F8" t="n">
-        <v>41.47574</v>
+        <v>42.19105</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05053</v>
+        <v>0.05042</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79721</v>
+        <v>1.83949</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.60564</v>
+        <v>16.80771</v>
       </c>
       <c r="D9" t="n">
-        <v>16.22923</v>
+        <v>16.09294</v>
       </c>
       <c r="E9" t="n">
-        <v>16.59475</v>
+        <v>16.65281</v>
       </c>
       <c r="F9" t="n">
-        <v>41.32435</v>
+        <v>41.98936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04975</v>
+        <v>0.0505</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79227</v>
+        <v>1.81215</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.64276</v>
+        <v>16.66023</v>
       </c>
       <c r="D10" t="n">
-        <v>16.09177</v>
+        <v>16.32906</v>
       </c>
       <c r="E10" t="n">
-        <v>16.78048</v>
+        <v>16.47341</v>
       </c>
       <c r="F10" t="n">
-        <v>42.04758</v>
+        <v>42.19194</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05045</v>
+        <v>0.04882</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81986</v>
+        <v>1.84499</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60445</v>
+        <v>0.60525</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13816</v>
+        <v>1.09555</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60072</v>
+        <v>0.60082</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1066</v>
+        <v>1.11059</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.59943</v>
+        <v>0.59523</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11323</v>
+        <v>1.09058</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.60451</v>
+        <v>0.6019099999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>1.10892</v>
+        <v>1.11163</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60383</v>
+        <v>0.60661</v>
       </c>
       <c r="D16" t="n">
-        <v>1.08839</v>
+        <v>1.09653</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.61327</v>
+        <v>0.60341</v>
       </c>
       <c r="D17" t="n">
-        <v>1.11215</v>
+        <v>1.09665</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.61265</v>
+        <v>0.59363</v>
       </c>
       <c r="D18" t="n">
-        <v>1.10347</v>
+        <v>1.07955</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60849</v>
+        <v>0.596</v>
       </c>
       <c r="D19" t="n">
-        <v>1.09879</v>
+        <v>1.10692</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.5913</v>
+        <v>0.60336</v>
       </c>
       <c r="D20" t="n">
-        <v>1.12822</v>
+        <v>1.09193</v>
       </c>
     </row>
   </sheetData>
